--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_buff_Calculation.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_buff_Calculation.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$E$8</definedName>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
   <si>
     <t>buff ID</t>
   </si>
@@ -105,7 +106,7 @@
     <t>生命之光</t>
   </si>
   <si>
-    <t>1000|10004#10000|10003#50000</t>
+    <t>1200|10004#10000|10003#50000</t>
   </si>
   <si>
     <t>守护之魂</t>
@@ -135,9 +136,6 @@
     </r>
   </si>
   <si>
-    <t>5|10003#1428</t>
-  </si>
-  <si>
     <t>战神之力</t>
   </si>
   <si>
@@ -170,6 +168,18 @@
   <si>
     <t>战神之力（精灵MM）</t>
   </si>
+  <si>
+    <t>致命圣印</t>
+  </si>
+  <si>
+    <t>500|10005#11111</t>
+  </si>
+  <si>
+    <t>5|10003#1428</t>
+  </si>
+  <si>
+    <t>1000|10004#10000|10003#50000</t>
+  </si>
 </sst>
 </file>
 
@@ -181,7 +191,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +207,12 @@
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -664,146 +680,149 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -816,9 +835,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -829,6 +845,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1366,211 +1388,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="17" style="3" customWidth="1"/>
-    <col min="2" max="2" width="18.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21.375" style="3" customWidth="1"/>
-    <col min="4" max="5" width="26.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="45.75" style="3" customWidth="1"/>
-    <col min="7" max="7" width="44.625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="17" style="4" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="4" customWidth="1"/>
+    <col min="4" max="5" width="26.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="45.75" style="4" customWidth="1"/>
+    <col min="7" max="7" width="44.625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="51" customHeight="1" spans="1:7">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="3" customFormat="1" ht="51" customHeight="1" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="7">
+      <c r="A5" s="2">
         <v>110000701</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="9">
         <v>1</v>
       </c>
       <c r="E5" s="10"/>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:7">
-      <c r="A6" s="7">
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="2">
         <v>120001101</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="9">
         <v>2</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="7">
+      <c r="A7" s="2">
         <v>130000401</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="9">
         <v>3</v>
       </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="7">
+      <c r="A8" s="2">
         <v>130000301</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="7">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2">
         <v>1</v>
       </c>
       <c r="D8" s="9">
         <v>4</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>28</v>
+      <c r="F8" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="7">
+      <c r="A9" s="2">
         <v>110000708</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="3">
+        <v>30</v>
+      </c>
+      <c r="C9" s="4">
         <v>2</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="7">
+      <c r="A10" s="2">
         <v>120001108</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="3">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4">
         <v>2</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>2</v>
       </c>
     </row>
@@ -1579,27 +1595,45 @@
         <v>130000408</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="3">
+        <v>32</v>
+      </c>
+      <c r="C11" s="4">
         <v>2</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="7">
+      <c r="A12" s="2">
         <v>130000308</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:7">
+      <c r="A13" s="12">
+        <v>101401012</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="3">
-        <v>2</v>
-      </c>
-      <c r="D12" s="3">
-        <v>4</v>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9">
+        <v>5</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="12" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1607,24 +1641,67 @@
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A9:B9">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:B10">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:D13">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:D8">
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" ht="15" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:1">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" ht="15" spans="1:1">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="15" spans="1:1">
+      <c r="A5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_buff_Calculation.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_buff_Calculation.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="36">
   <si>
     <t>buff ID</t>
   </si>
@@ -173,12 +173,6 @@
   </si>
   <si>
     <t>500|10005#11111</t>
-  </si>
-  <si>
-    <t>5|10003#1428</t>
-  </si>
-  <si>
-    <t>1000|10004#10000|10003#50000</t>
   </si>
 </sst>
 </file>
@@ -817,23 +811,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1391,241 +1385,249 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="17" style="4" customWidth="1"/>
-    <col min="2" max="2" width="18.125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="21.375" style="4" customWidth="1"/>
-    <col min="4" max="5" width="26.375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="45.75" style="4" customWidth="1"/>
+    <col min="1" max="1" width="17" style="3" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="3" customWidth="1"/>
+    <col min="4" max="5" width="26.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="45.75" style="3" customWidth="1"/>
     <col min="7" max="7" width="44.625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="1" ht="51" customHeight="1" spans="1:7">
-      <c r="A2" s="4" t="s">
+    <row r="2" s="2" customFormat="1" ht="51" customHeight="1" spans="1:7">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:7">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="4" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2">
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="A5" s="7">
         <v>110000701</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="7">
         <v>1</v>
       </c>
       <c r="D5" s="9">
         <v>1</v>
       </c>
       <c r="E5" s="10"/>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
-      <c r="A6" s="2">
+      <c r="A6" s="7">
         <v>120001101</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="9">
         <v>2</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2">
+    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="A7" s="7">
         <v>130000401</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="9">
         <v>3</v>
       </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
+    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="A8" s="7">
         <v>130000301</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="9">
         <v>4</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2">
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="A9" s="7">
         <v>110000708</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>2</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="A10" s="7">
         <v>120001108</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>2</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:7">
       <c r="A11" s="11">
         <v>130000408</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>2</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="A12" s="7">
         <v>130000308</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>2</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:7">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:7">
       <c r="A13" s="12">
         <v>101401012</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="7">
         <v>1</v>
       </c>
       <c r="D13" s="9">
@@ -1641,19 +1643,19 @@
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A9:B9">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10:B10">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:B12">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -1662,7 +1664,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:D8">
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1672,35 +1674,287 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="17" style="3" customWidth="1"/>
+    <col min="2" max="2" width="18.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21.375" style="3" customWidth="1"/>
+    <col min="4" max="5" width="26.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="45.75" style="3" customWidth="1"/>
+    <col min="7" max="7" width="44.625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" ht="15" spans="1:1">
-      <c r="A2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" ht="15" spans="1:1">
-      <c r="A3" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="51" customHeight="1" spans="1:7">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:7">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="A5" s="7">
+        <v>110000701</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="A6" s="7">
+        <v>120001101</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="1:1">
-      <c r="A4" s="2" t="s">
+    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="A7" s="7">
+        <v>130000401</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9">
+        <v>3</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="1:1">
-      <c r="A5" s="2" t="s">
+    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="A8" s="7">
+        <v>130000301</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9">
+        <v>4</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
     </row>
+    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="A9" s="7">
+        <v>110000708</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="A10" s="7">
+        <v>120001108</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:7">
+      <c r="A11" s="11">
+        <v>130000408</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="A12" s="7">
+        <v>130000308</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:7">
+      <c r="A13" s="12">
+        <v>101401012</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9">
+        <v>5</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A9:B9">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10:B10">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12:B12">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:D13">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:D8">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
